--- a/server/data/tpl2026.xlsx
+++ b/server/data/tpl2026.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -532,9 +532,71 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TPL26-P002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>jhgfd</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>9876543211</v>
+      </c>
+      <c r="G3" t="str">
+        <v>hh@gmail.com</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v>Bowler</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>2026-09-18T17:53:48.539Z</v>
+      </c>
+      <c r="R3" t="str">
+        <v>REGISTERED</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1054,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1264,9 +1326,35 @@
         <v>admin</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3d9893d5-85dd-46b1-875f-2484a2ef1e17</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PLAYER_REGISTERED</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Player</v>
+      </c>
+      <c r="D9" t="str">
+        <v>TPL26-P002</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>REGISTERED</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-09-18T17:53:48.576Z</v>
+      </c>
+      <c r="H9" t="str">
+        <v>public</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
   </ignoredErrors>
 </worksheet>
 </file>
